--- a/selenium_model/VALIDATION_TESTING_350_REPORT.xlsx
+++ b/selenium_model/VALIDATION_TESTING_350_REPORT.xlsx
@@ -4863,7 +4863,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F218" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F293" t="n">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F322" t="n">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F335" t="n">
